--- a/test.xlsx
+++ b/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,15 +486,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>word_group</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>n_unique_words</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>bitwise_or</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>bitwise_and</t>
         </is>
@@ -546,13 +551,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>5</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M2" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -602,13 +612,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>5</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M3" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -658,13 +673,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>5</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M4" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -714,13 +734,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>5</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M5" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,13 +795,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>5</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M6" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -826,13 +856,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>5</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M7" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -882,13 +917,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>5</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M8" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -938,13 +978,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>5</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M9" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,13 +1039,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>5</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M10" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1050,13 +1100,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>5</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M11" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1106,13 +1161,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>5</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M12" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1162,13 +1222,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>5</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M13" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1218,13 +1283,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>5</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M14" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1274,13 +1344,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>5</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M15" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1330,13 +1405,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>5</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M16" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,13 +1466,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>5</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M17" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1442,13 +1527,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>5</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M18" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1498,13 +1588,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>5</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M19" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1554,13 +1649,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>5</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M20" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1610,13 +1710,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>5</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M21" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1666,13 +1771,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>5</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M22" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1722,13 +1832,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>5</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M23" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1778,13 +1893,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>5</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M24" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1834,13 +1954,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>5</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M25" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1890,13 +2015,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>5</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M26" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1946,13 +2076,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>5</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M27" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2002,13 +2137,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>5</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M28" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2058,13 +2198,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>5</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M29" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2114,13 +2259,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>5</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M30" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2170,13 +2320,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>5</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M31" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2226,13 +2381,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>5</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M32" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2282,13 +2442,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>5</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M33" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2338,13 +2503,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>5</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M34" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2394,13 +2564,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>5</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M35" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2450,13 +2625,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>5</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M36" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2506,13 +2686,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>5</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M37" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2562,13 +2747,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>5</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M38" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2618,13 +2808,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>5</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M39" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2674,13 +2869,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>5</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M40" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2730,13 +2930,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>5</v>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M41" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2786,13 +2991,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>5</v>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M42" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2842,13 +3052,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>5</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M43" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2898,13 +3113,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>5</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M44" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2954,13 +3174,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>5</v>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M45" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3010,13 +3235,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>5</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M46" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3066,13 +3296,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>5</v>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M47" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3122,13 +3357,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>5</v>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M48" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3178,13 +3418,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>5</v>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M49" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3234,13 +3479,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>5</v>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M50" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3290,13 +3540,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>5</v>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M51" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3346,13 +3601,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>5</v>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M52" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3402,13 +3662,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>5</v>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M53" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3458,13 +3723,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>5</v>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>bizen fldxt gravy jocks whump</t>
+        </is>
       </c>
       <c r="M54" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3514,13 +3784,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L55" t="n">
-        <v>5</v>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M55" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3570,13 +3845,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>5</v>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M56" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3626,13 +3906,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>5</v>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M57" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3682,13 +3967,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>5</v>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M58" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3738,13 +4028,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>5</v>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M59" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3794,13 +4089,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>5</v>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M60" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3850,13 +4150,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>5</v>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>fldxt jocks verby whump zigan</t>
+        </is>
       </c>
       <c r="M61" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3906,13 +4211,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>5</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M62" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3962,13 +4272,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L63" t="n">
-        <v>5</v>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M63" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4018,13 +4333,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>5</v>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>dwarf glyph jocks muntz vibex</t>
+        </is>
       </c>
       <c r="M64" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4074,13 +4394,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>5</v>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M65" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4130,13 +4455,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>5</v>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M66" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4186,13 +4516,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L67" t="n">
-        <v>5</v>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M67" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4242,13 +4577,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L68" t="n">
-        <v>5</v>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M68" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4298,13 +4638,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L69" t="n">
-        <v>5</v>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>burez fldxt jocks vying whamp</t>
+        </is>
       </c>
       <c r="M69" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4354,13 +4699,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L70" t="n">
-        <v>5</v>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>braze fldxt jocks vying whump</t>
+        </is>
       </c>
       <c r="M70" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N70" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4410,13 +4760,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>5</v>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M71" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4466,13 +4821,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L72" t="n">
-        <v>5</v>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M72" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4522,13 +4882,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L73" t="n">
-        <v>5</v>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>bumph fldxt gravy jocks winze</t>
+        </is>
       </c>
       <c r="M73" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4578,13 +4943,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>5</v>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M74" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4634,13 +5004,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L75" t="n">
-        <v>5</v>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M75" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N75" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4690,13 +5065,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L76" t="n">
-        <v>5</v>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks wyver zigan</t>
+        </is>
       </c>
       <c r="M76" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N76" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4746,13 +5126,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L77" t="n">
-        <v>5</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M77" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4802,13 +5187,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L78" t="n">
-        <v>5</v>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M78" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N78" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4858,13 +5248,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>5</v>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M79" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N79" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4914,13 +5309,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>5</v>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M80" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N80" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4970,13 +5370,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>5</v>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>bumph fldxt jocks warve zingy</t>
+        </is>
       </c>
       <c r="M81" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N81" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5026,13 +5431,18 @@
           <t>q</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>5</v>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>brave fldxt jocks whump zingy</t>
+        </is>
       </c>
       <c r="M82" t="n">
-        <v>67043327</v>
+        <v>5</v>
       </c>
       <c r="N82" t="n">
+        <v>67043327</v>
+      </c>
+      <c r="O82" t="n">
         <v>0</v>
       </c>
     </row>
